--- a/_01_main/_05_validation/DL_renaming_test_names.xlsx
+++ b/_01_main/_05_validation/DL_renaming_test_names.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\davis\00_data\01_Projects\Personal\SCDL\_01_main\_02_tests\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\davis\00_data\01_Projects\Personal\SCDL\_01_main\_05_validation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3973B6D-DAF4-4072-8204-7979F570DD10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687FD6E1-AD42-4B7E-A909-F5BDFA4D4DC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="9810" windowHeight="15855" xr2:uid="{9664D8D8-E09F-4482-9132-8996544CFBDA}"/>
+    <workbookView xWindow="4290" yWindow="4290" windowWidth="28800" windowHeight="15555" xr2:uid="{9664D8D8-E09F-4482-9132-8996544CFBDA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>Soundcloud name</t>
   </si>
@@ -120,6 +120,18 @@
   </si>
   <si>
     <t>Ashanti_-_Only_U_Darkzy_RemixFree_Download</t>
+  </si>
+  <si>
+    <t>The_Prodigy_-_Breathe_Psychodrums_Mr_Dj_HT_REWORK_FREE_DOWNLOAD</t>
+  </si>
+  <si>
+    <t>The Prodigy - Breathe (Psychodrums &amp; Mr Dj HT REWORK) {FREE DOWNLOAD}</t>
+  </si>
+  <si>
+    <t>2Passey - HOW WE DO (50 Cent Trance Edit) (FREE DL&lt;3)</t>
+  </si>
+  <si>
+    <t>2Passey_-_HOW_WE_DO_50_Cent_Trance_Edit_FREE_DL3</t>
   </si>
 </sst>
 </file>
@@ -172,6 +184,17 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1FE83341-305B-4BD8-B61B-BA5CB9828B4E}" name="Table1" displayName="Table1" ref="A1:B16" totalsRowShown="0">
+  <autoFilter ref="A1:B16" xr:uid="{1FE83341-305B-4BD8-B61B-BA5CB9828B4E}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{F257B44C-BF51-4562-94BA-BF688BC90EC3}" name="Soundcloud name"/>
+    <tableColumn id="2" xr3:uid="{27135CEA-522C-448A-A3E4-349C59F888E8}" name="Download Name"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -491,8 +514,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C28437CC-2DD0-43B3-B933-50C4FE5FA466}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="48.85546875" customWidth="1"/>
+    <col min="2" max="2" width="54.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -606,7 +633,26 @@
         <v>27</v>
       </c>
     </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>29</v>
+      </c>
+      <c r="B15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>30</v>
+      </c>
+      <c r="B16" t="s">
+        <v>31</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>